--- a/data/attendance/ECOLE_نذير_رياضي.xlsx
+++ b/data/attendance/ECOLE_نذير_رياضي.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:75ece5c5-7faf-4db4-8ce1-ff608e6170e9</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b3d0d8da-8766-4966-8b8b-c40c44d1d6a7</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:25358248-ee8d-47df-b4b6-3ab011f7f445</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4c2714a1-2de7-43b7-bc98-7f712a191a29</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c3ff4d17-8564-4787-8334-e693580d852a</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d8da6d91-e82a-403d-be1c-7379d8f3f360</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b5434f48-2bed-43a0-ada7-62bd10b64a5e</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:fe3df352-d086-4e10-8e32-c1ba9ff264ac</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e81e85b7-69ed-4e8f-af03-4a19f1f7a646</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:5ca01918-1146-4301-9482-0fd8f6f2b9e1</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4b3fa311-5a32-48a1-b54c-1490ca4870b3</t>
         </r>
       </text>
@@ -177,111 +97,55 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+          <t>student_id:48a125fe-bb69-4b34-8dd8-b357f3776ad2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
           <t>student_id:d84eb3f6-2641-478a-9141-45f743f95415</t>
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
           <t>student_id:2adb635a-c5f8-47dd-a2ce-171b755990cb</t>
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
           <t>student_id:7f304429-1bb8-4a12-b67b-a06b8388ceca</t>
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
           <t>student_id:4018fc76-adc8-4b6e-84d6-0bacbec4c62b</t>
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
           <t>student_id:bd1af0ef-db31-4469-9812-a9ebea743880</t>
         </r>
       </text>
     </comment>
-    <comment ref="B21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
           <t>student_id:cf423c40-e6cf-4565-9a1c-2dc7a984baf3</t>
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:430f237a-f440-498e-954b-daa1e7e67101</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:874f8dc6-883a-43e7-83e8-643c79aaa4fb</t>
         </r>
       </text>
@@ -289,13 +153,6 @@
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:eca20f66-1951-4880-9cf2-2c0a0afd766e</t>
         </r>
       </text>
@@ -303,13 +160,6 @@
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a99fe64e-33c6-4062-9e79-7dd72d8cb65e</t>
         </r>
       </text>
@@ -317,13 +167,6 @@
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4296455c-e7fb-4a66-9751-cd36ffdf92ae</t>
         </r>
       </text>
@@ -331,13 +174,6 @@
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:53568b03-4e77-4008-9501-55326a5b9087</t>
         </r>
       </text>
@@ -345,13 +181,6 @@
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:3e9560ca-56b1-4f0d-ab49-2372b3b66c0d</t>
         </r>
       </text>
@@ -359,13 +188,6 @@
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:04e260a5-0659-47c5-82e5-d3a945c1ecd0</t>
         </r>
       </text>
@@ -373,13 +195,6 @@
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c54885de-04ca-4ca5-b191-6794daf17b8c</t>
         </r>
       </text>
@@ -387,13 +202,6 @@
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4b6d8411-87c2-4fde-8d61-9997674732b0</t>
         </r>
       </text>
@@ -401,13 +209,6 @@
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a45b56ca-5e6d-4388-9def-87f2601942c5</t>
         </r>
       </text>
@@ -415,13 +216,6 @@
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e24743ff-6a7f-497c-a9bc-04e96c8bb83a</t>
         </r>
       </text>
@@ -429,13 +223,6 @@
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6df4572b-ca54-4578-8cb1-f0e9525f5b8c</t>
         </r>
       </text>
@@ -443,13 +230,6 @@
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e802c634-d32a-4ac8-b0b2-17f5e1ae768b</t>
         </r>
       </text>
@@ -457,13 +237,6 @@
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:23bdc4b1-268a-4944-8a3a-68e998a1b5d4</t>
         </r>
       </text>
@@ -471,13 +244,6 @@
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b1b33475-c26e-4b5c-9269-94bf2515d315</t>
         </r>
       </text>
@@ -485,13 +251,6 @@
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:71b680a6-b209-403d-8ae9-141d00a50dea</t>
         </r>
       </text>
@@ -499,13 +258,6 @@
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:db80e6bb-d006-49c2-9e13-baf7d7f4c51c</t>
         </r>
       </text>
@@ -513,13 +265,6 @@
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:bc21892c-9808-4a68-8349-c5c4aacb0cb7</t>
         </r>
       </text>
@@ -527,13 +272,6 @@
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:13cb89b1-d42d-428d-af65-31fea727c2b0</t>
         </r>
       </text>
@@ -541,13 +279,6 @@
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d35e0b69-924f-4570-9109-0638c493ab00</t>
         </r>
       </text>
@@ -555,13 +286,6 @@
     <comment ref="B43" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1fae5d56-f4a5-474b-91ac-1ee9d6eb2290</t>
         </r>
       </text>
@@ -569,13 +293,6 @@
     <comment ref="B44" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:496982a0-23c4-4e33-b9cc-527a3645471a</t>
         </r>
       </text>
@@ -583,13 +300,6 @@
     <comment ref="B45" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b53ce4cc-85b1-4d37-ab4d-c38e771590d1</t>
         </r>
       </text>
@@ -599,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
   <si>
     <t>نذير رياضي  |  ECOLE  |  BAC  |  بوعبدالله نذير</t>
   </si>
@@ -613,6 +323,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -637,6 +350,9 @@
     <t>20/09/2026</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -673,6 +389,9 @@
     <t>زعتري طه</t>
   </si>
   <si>
+    <t>فداوي نارادين</t>
+  </si>
+  <si>
     <t>سليمي اسراء</t>
   </si>
   <si>
@@ -691,9 +410,6 @@
     <t>غبيش عبد المغيث</t>
   </si>
   <si>
-    <t>فداوي ناردين</t>
-  </si>
-  <si>
     <t>لوصيف أمينة وصال</t>
   </si>
   <si>
@@ -790,7 +506,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -812,40 +531,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -932,7 +644,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1288,14 +1000,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1025,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1323,10 +1035,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1368,69 +1083,69 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
         <v>0</v>
       </c>
       <c r="F5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8">
         <v>0</v>
@@ -1454,27 +1169,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>67</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1498,27 +1213,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>117</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8">
         <v>0</v>
@@ -1542,12 +1257,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>118</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1562,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1586,27 +1301,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>124</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
@@ -1630,27 +1345,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>125</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1674,27 +1389,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>126</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8">
         <v>0</v>
@@ -1718,24 +1433,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>128</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
@@ -1762,24 +1477,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>129</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="8">
         <v>0</v>
@@ -1806,12 +1521,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>132</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1820,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1850,27 +1565,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>133</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
@@ -1894,291 +1609,291 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
+        <v>136</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>140</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="B17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>142</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1</v>
-      </c>
-      <c r="G17" s="8">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="B18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>149</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="B19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>158</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="B20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>164</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="B21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>195</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1</v>
-      </c>
-      <c r="G21" s="8">
-        <v>1</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>651</v>
-      </c>
       <c r="B22" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2202,27 +1917,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>652</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="8">
         <v>0</v>
@@ -2246,27 +1961,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>653</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2290,27 +2005,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>654</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8">
         <v>0</v>
@@ -2334,27 +2049,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>655</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" s="9">
         <v>0</v>
       </c>
       <c r="D26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="9">
         <v>0</v>
       </c>
       <c r="F26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2378,27 +2093,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>656</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="8">
         <v>0</v>
@@ -2422,27 +2137,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>657</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2466,24 +2181,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>658</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="8">
         <v>0</v>
@@ -2510,27 +2225,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>659</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2554,27 +2269,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>660</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="8">
         <v>0</v>
@@ -2598,15 +2313,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>661</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
@@ -2642,27 +2357,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>662</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="8">
         <v>0</v>
@@ -2686,27 +2401,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>663</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2730,27 +2445,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>664</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="8">
         <v>0</v>
@@ -2774,24 +2489,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>665</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C36" s="9">
         <v>0</v>
       </c>
       <c r="D36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="9">
         <v>0</v>
@@ -2818,27 +2533,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>666</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C37" s="8">
         <v>0</v>
       </c>
       <c r="D37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="8">
         <v>0</v>
@@ -2862,12 +2577,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>667</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C38" s="9">
         <v>0</v>
@@ -2876,13 +2591,13 @@
         <v>0</v>
       </c>
       <c r="E38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -2906,27 +2621,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>668</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="8">
         <v>0</v>
@@ -2950,12 +2665,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>669</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C40" s="9">
         <v>0</v>
@@ -2964,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -2994,12 +2709,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>670</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" s="8">
         <v>0</v>
@@ -3008,13 +2723,13 @@
         <v>0</v>
       </c>
       <c r="E41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="8">
         <v>0</v>
@@ -3038,27 +2753,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>671</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3082,12 +2797,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>672</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C43" s="8">
         <v>0</v>
@@ -3099,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="8">
         <v>0</v>
@@ -3126,27 +2841,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>673</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3170,27 +2885,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>674</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8">
         <v>0</v>
@@ -3220,7 +2935,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -3230,89 +2945,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>